--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/call_center-1000j-100m-2_30tr-same_per_machined-20c_sjf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/call_center-1000j-100m-2_30tr-same_per_machined-20c_sjf.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,334 +458,334 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>849-633-3600</t>
+          <t>849-202-1113</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alicia Luz</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>849-468-9418</t>
+          <t>849-274-9481</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alicia Luz</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>809-958-2619</t>
+          <t>829-294-6191</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alicia Luz</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>849-657-4659</t>
+          <t>809-709-3050</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alicia Luz</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>809-873-1325</t>
+          <t>849-779-8275</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alicia Luz</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>809-486-5156</t>
+          <t>849-968-1425</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alicia Luz</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>809-879-6248</t>
+          <t>849-412-5080</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Juan Arboleda</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>849-224-3947</t>
+          <t>849-311-3144</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Juan Arboleda</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>849-911-5600</t>
+          <t>849-258-6587</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Juan Arboleda</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>829-679-5610</t>
+          <t>849-268-8332</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Juan Arboleda</t>
+          <t>Antonia Lozano</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>809-510-5899</t>
+          <t>829-277-6961</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Juan Arboleda</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>809-435-3364</t>
+          <t>829-272-6537</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Juan Arboleda</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>829-626-2085</t>
+          <t>829-251-2094</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Antonio José</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>849-668-6395</t>
+          <t>809-536-8060</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Antonio José</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>809-974-8723</t>
+          <t>849-772-4638</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Antonio José</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>849-798-3277</t>
+          <t>809-641-6553</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Antonio José</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
@@ -794,208 +794,208 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>809-690-5569</t>
+          <t>809-973-5635</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Antonio José</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>849-292-7430</t>
+          <t>849-252-2435</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Antonio José</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>829-908-4750</t>
+          <t>809-939-3000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gerardo Rosero</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>809-218-3823</t>
+          <t>809-252-9356</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gerardo Rosero</t>
+          <t>Sandra Díaz</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>829-525-2577</t>
+          <t>829-353-5645</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gerardo Rosero</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>809-495-9903</t>
+          <t>809-665-5585</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gerardo Rosero</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
         <v>4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>12</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>849-758-7384</t>
+          <t>829-811-2282</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gerardo Rosero</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
-        <v>16</v>
-      </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>829-490-8838</t>
+          <t>829-832-9921</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rodolfo Acevedo</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>809-738-3976</t>
+          <t>809-729-8958</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rodolfo Acevedo</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>809-935-2594</t>
+          <t>829-609-4354</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rodolfo Acevedo</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
@@ -1004,250 +1004,250 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>829-568-7957</t>
+          <t>829-887-3710</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rodolfo Acevedo</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>849-296-1422</t>
+          <t>829-223-2155</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rodolfo Acevedo</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" t="n">
         <v>16</v>
-      </c>
-      <c r="E29" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>809-477-5648</t>
+          <t>849-771-2410</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ángel Miguel</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>809-938-8448</t>
+          <t>809-297-1825</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ángel Miguel</t>
+          <t>María Liliana</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>849-500-1511</t>
+          <t>849-835-1120</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ángel Miguel</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>849-221-6319</t>
+          <t>809-467-8488</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ángel Miguel</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>829-299-5471</t>
+          <t>829-799-5109</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ángel Miguel</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>809-229-8892</t>
+          <t>809-538-5500</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ángel Miguel</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>849-443-1621</t>
+          <t>809-211-1547</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>809-787-5454</t>
+          <t>849-998-8564</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>809-601-9762</t>
+          <t>849-894-9487</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>809-351-2921</t>
+          <t>849-579-1828</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E39" t="n">
         <v>16</v>
@@ -1256,670 +1256,670 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>849-427-1891</t>
+          <t>809-251-6515</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jesús David</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>829-811-6334</t>
+          <t>849-290-2341</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alberto David</t>
+          <t>César Leandro</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>849-917-1926</t>
+          <t>829-660-4297</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alberto David</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>809-667-8653</t>
+          <t>809-997-5945</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alberto David</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>849-986-9553</t>
+          <t>849-840-9656</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alberto David</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>809-942-1525</t>
+          <t>829-665-1843</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Alberto David</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>849-792-6403</t>
+          <t>829-628-7732</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alba Milena</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>849-860-5057</t>
+          <t>829-469-4582</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alba Milena</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E47" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>829-345-5466</t>
+          <t>849-835-7375</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alba Milena</t>
+          <t>Marina Bedoya</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>849-793-2596</t>
+          <t>829-234-4994</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alba Milena</t>
+          <t>Marina Bedoya</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>809-841-8268</t>
+          <t>809-484-4304</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alba Milena</t>
+          <t>Marina Bedoya</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>849-398-6533</t>
+          <t>809-475-3208</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adriana Medina</t>
+          <t>Marina Bedoya</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>809-238-7470</t>
+          <t>829-498-9188</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Adriana Medina</t>
+          <t>Marina Bedoya</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>829-690-8731</t>
+          <t>809-419-1285</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Adriana Medina</t>
+          <t>Marina Bedoya</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>809-649-8863</t>
+          <t>809-265-3383</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adriana Medina</t>
+          <t>Nancy Mosquera</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>829-651-9902</t>
+          <t>829-769-1247</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jhoana Valencia</t>
+          <t>Nancy Mosquera</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>829-965-6636</t>
+          <t>809-661-3732</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jhoana Valencia</t>
+          <t>Nancy Mosquera</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>849-636-5440</t>
+          <t>829-951-5494</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jhoana Valencia</t>
+          <t>Nancy Mosquera</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>829-395-8316</t>
+          <t>809-311-8187</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jhoana Valencia</t>
+          <t>Nancy Mosquera</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
+        <v>12</v>
+      </c>
+      <c r="E58" t="n">
         <v>15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>829-608-2542</t>
+          <t>829-908-4019</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Nancy Mosquera</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>829-584-2227</t>
+          <t>849-702-8087</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Ángel Jimmy</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>849-910-7014</t>
+          <t>809-584-2136</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Ángel Jimmy</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>849-896-8661</t>
+          <t>829-970-2885</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Enrique Orlando</t>
+          <t>Ángel Jimmy</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>849-317-3311</t>
+          <t>829-294-5182</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Yineth Ruiz</t>
+          <t>Ángel Jimmy</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>829-777-7139</t>
+          <t>829-308-5214</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Yineth Ruiz</t>
+          <t>Ángel Jimmy</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>829-676-7314</t>
+          <t>829-543-8267</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yineth Ruiz</t>
+          <t>Vanessa Ortiz</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>829-465-9822</t>
+          <t>809-862-2541</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Yineth Ruiz</t>
+          <t>Vanessa Ortiz</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>809-662-2630</t>
+          <t>849-355-9755</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Yineth Ruiz</t>
+          <t>Vanessa Ortiz</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>809-538-2021</t>
+          <t>849-648-3768</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gabriela Fernanda</t>
+          <t>Vanessa Ortiz</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>809-579-3676</t>
+          <t>809-434-9803</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gabriela Fernanda</t>
+          <t>Vanessa Ortiz</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>829-272-5210</t>
+          <t>849-882-8713</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gabriela Fernanda</t>
+          <t>Leidy María</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>809-313-4272</t>
+          <t>809-616-7278</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rocío Consuelo</t>
+          <t>Leidy María</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
         <v>6</v>
@@ -1928,180 +1928,180 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>849-347-3997</t>
+          <t>849-938-6757</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rocío Consuelo</t>
+          <t>Leidy María</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>6</v>
       </c>
       <c r="E72" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>829-727-5579</t>
+          <t>829-842-4093</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rocío Consuelo</t>
+          <t>Leidy María</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>849-992-3248</t>
+          <t>809-487-7046</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Leidy María</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>829-311-4600</t>
+          <t>829-312-4084</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Leidy María</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>809-293-2255</t>
+          <t>849-328-2144</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fabián Fernández</t>
+          <t>Margarita Vásquez</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>849-881-1112</t>
+          <t>809-876-9960</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Liliana Arévalo</t>
+          <t>Margarita Vásquez</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>849-278-4989</t>
+          <t>809-762-6058</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Liliana Arévalo</t>
+          <t>Margarita Vásquez</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>849-811-6386</t>
+          <t>829-615-5089</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Liliana Arévalo</t>
+          <t>Margarita Vásquez</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E79" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>809-680-2618</t>
+          <t>809-765-1563</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Eugenia Quintero</t>
+          <t>Elizabeth Gabriela</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2117,12 +2117,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>829-393-2358</t>
+          <t>849-580-8817</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Eugenia Quintero</t>
+          <t>Elizabeth Gabriela</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2138,12 +2138,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>849-551-4131</t>
+          <t>809-672-7837</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Eugenia Quintero</t>
+          <t>Elizabeth Gabriela</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2159,12 +2159,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>849-426-3697</t>
+          <t>849-590-6829</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eugenia Quintero</t>
+          <t>Elizabeth Gabriela</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2180,82 +2180,82 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>809-932-8181</t>
+          <t>849-991-5841</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abel Juan</t>
+          <t>Luz Andrea</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>849-381-8477</t>
+          <t>829-281-8473</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abel Juan</t>
+          <t>Luz Andrea</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>849-504-9484</t>
+          <t>809-831-8374</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Libardo Adolfo</t>
+          <t>Luz Andrea</t>
         </is>
       </c>
       <c r="C86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" t="n">
         <v>8</v>
       </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
       <c r="E86" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>829-269-8088</t>
+          <t>849-514-3882</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Libardo Adolfo</t>
+          <t>Luz Andrea</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E87" t="n">
         <v>16</v>
@@ -2264,313 +2264,313 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>809-379-1337</t>
+          <t>829-981-4957</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Manuel Norberto</t>
+          <t>Luz Andrea</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>829-365-3999</t>
+          <t>809-931-2011</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Manuel Norberto</t>
+          <t>Viviana Sofía</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>849-446-6926</t>
+          <t>849-532-3548</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Estella Estella</t>
+          <t>Viviana Sofía</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>829-378-9416</t>
+          <t>809-731-1919</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Estella Estella</t>
+          <t>Viviana Sofía</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>809-735-9883</t>
+          <t>809-777-3301</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ángela Sánchez</t>
+          <t>David Arturo</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>849-861-6051</t>
+          <t>849-629-2401</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ángela Sánchez</t>
+          <t>David Arturo</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>809-406-3665</t>
+          <t>849-474-2944</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clemencia Maricela</t>
+          <t>David Arturo</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>849-296-6426</t>
+          <t>849-798-9559</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Clemencia Maricela</t>
+          <t>María Vanessa</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>849-451-5409</t>
+          <t>809-333-4387</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Manuel Ortiz</t>
+          <t>María Vanessa</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>829-611-1710</t>
+          <t>809-963-8150</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Manuel Ortiz</t>
+          <t>María Vanessa</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E97" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>809-766-1726</t>
+          <t>849-913-4195</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Paola Díaz</t>
+          <t>Alexander Emiro</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>829-428-6741</t>
+          <t>809-503-5785</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Luis Hernando</t>
+          <t>Alexander Emiro</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>829-284-3629</t>
+          <t>849-615-8969</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alexander Anaya</t>
+          <t>Alexander Emiro</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>809-443-9197</t>
+          <t>849-766-1820</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Javier Marco</t>
+          <t>Efrén Arturo</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>829-522-4515</t>
+          <t>829-805-8438</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Margarita Judith</t>
+          <t>Efrén Arturo</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
         <v>10</v>
@@ -2579,229 +2579,229 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>829-473-8921</t>
+          <t>829-740-1320</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Margarita Judith</t>
+          <t>Efrén Arturo</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
         <v>10</v>
       </c>
       <c r="E103" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>849-362-8367</t>
+          <t>829-723-5351</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Patricia Graciela</t>
+          <t>Efrén Arturo</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>849-680-7051</t>
+          <t>829-766-4425</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Patricia Graciela</t>
+          <t>Sandra Toro</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>829-265-1463</t>
+          <t>809-700-4947</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Laura Ortega</t>
+          <t>Sandra Toro</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>809-281-7941</t>
+          <t>809-422-5004</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Laura Ortega</t>
+          <t>Alcira Lady</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>829-481-2380</t>
+          <t>809-217-6734</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Luis Andrés</t>
+          <t>Alcira Lady</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>829-395-2839</t>
+          <t>829-886-7182</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Luis Andrés</t>
+          <t>María Pinzón</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>829-448-7510</t>
+          <t>809-464-5828</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Giovanny Enrique</t>
+          <t>María Pinzón</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>849-521-8589</t>
+          <t>829-972-2695</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Giovanny Enrique</t>
+          <t>Alberto Cerón</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>849-666-7236</t>
+          <t>809-390-5337</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Emilio Salgado</t>
+          <t>Alberto Cerón</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>829-416-7525</t>
+          <t>829-504-5105</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Emilio Salgado</t>
+          <t>Alberto Cerón</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D113" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E113" t="n">
         <v>18</v>
@@ -2810,861 +2810,1680 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>829-873-1875</t>
+          <t>849-378-4849</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Clara García</t>
+          <t>Cindy Shirley</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>849-721-8730</t>
+          <t>809-423-8773</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Edilma Barrios</t>
+          <t>Cindy Shirley</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E115" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>829-713-7834</t>
+          <t>849-875-2635</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Alberto Rafael</t>
+          <t>Cindy Shirley</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>809-734-5025</t>
+          <t>849-648-9602</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marcela Leidy</t>
+          <t>Carlos Trujillo</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>809-850-4258</t>
+          <t>829-845-4774</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Julio José</t>
+          <t>Carlos Trujillo</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E118" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>809-644-5373</t>
+          <t>809-656-6879</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mauricio Rivera</t>
+          <t>Carlos Trujillo</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E119" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>809-895-5242</t>
+          <t>829-671-8478</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Luis Julián</t>
+          <t>Graciela Suárez</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>809-772-7357</t>
+          <t>849-796-9126</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Alberto Salazar</t>
+          <t>Graciela Suárez</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E121" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>849-805-1111</t>
+          <t>809-456-5687</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>David Saavedra</t>
+          <t>Juan Mendoza</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>849-261-4150</t>
+          <t>829-265-5303</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Andrés Ortiz</t>
+          <t>Juan Mendoza</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>829-929-9376</t>
+          <t>829-416-2187</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Alberto Mauricio</t>
+          <t>Danilo Cabrera</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>849-450-8884</t>
+          <t>809-740-1029</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Karina Liliana</t>
+          <t>Danilo Cabrera</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E125" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>849-395-2867</t>
+          <t>849-757-2337</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Francisco Sebastián</t>
+          <t>Martha Mariana</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>849-643-6375</t>
+          <t>849-966-2621</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Fernando Hernández</t>
+          <t>Martha Mariana</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E127" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>829-720-9876</t>
+          <t>809-661-1532</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Yulieth Vélez</t>
+          <t>Edgar Rojas</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>829-504-1999</t>
+          <t>849-701-1503</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Carolina Alejandra</t>
+          <t>Edgar Rojas</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E129" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>809-806-1821</t>
+          <t>809-769-3219</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Wilmer Rubio</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>849-988-1347</t>
+          <t>849-866-4846</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Johana Barrios</t>
+          <t>Clara Triana</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E131" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>849-788-8482</t>
+          <t>809-670-4998</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Carolina Ríos</t>
+          <t>Andrea Mercedes</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>849-346-3187</t>
+          <t>809-760-9774</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Aurora Clara</t>
+          <t>Andrea Mercedes</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E133" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>849-711-6753</t>
+          <t>809-831-6128</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>David Fernando</t>
+          <t>Francisco Alfonso</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>829-292-6999</t>
+          <t>829-411-3881</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Eliana Pérez</t>
+          <t>Francisco Alfonso</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E135" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>829-717-6773</t>
+          <t>849-440-8757</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>José Daza</t>
+          <t>Luis Ortiz</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>809-749-5019</t>
+          <t>809-736-9065</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Andrea Marín</t>
+          <t>Andrea Fuentes</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>849-835-5493</t>
+          <t>809-958-4021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Alejandra Quintero</t>
+          <t>Mónica Ramírez</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>829-922-6748</t>
+          <t>829-292-6107</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Julián Velásquez</t>
+          <t>Juliana Sánchez</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>829-828-6821</t>
+          <t>829-936-6178</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Julián Velásquez</t>
+          <t>Marcela Blanca</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>849-687-6141</t>
+          <t>849-295-9152</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Julián Velásquez</t>
+          <t>Stella María</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>849-727-9923</t>
+          <t>849-570-8617</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Julián Velásquez</t>
+          <t>Ernesto Carlos</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D142" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>809-897-1108</t>
+          <t>829-970-5050</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Julián Velásquez</t>
+          <t>Cristian Felipe</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D143" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>849-325-6363</t>
+          <t>809-358-3674</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Julián Velásquez</t>
+          <t>Lucía Guzmán</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D144" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>809-851-8632</t>
+          <t>829-696-1890</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>René Gustavo</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>849-235-5984</t>
+          <t>849-229-4319</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Martha María</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>809-937-9315</t>
+          <t>849-565-5904</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Martha María</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E147" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>809-269-2828</t>
+          <t>849-848-9125</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Aurora Marcela</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>849-530-4096</t>
+          <t>809-790-3766</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Aurora Marcela</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D149" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E149" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>849-300-8530</t>
+          <t>849-284-8298</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Milena Yaneth</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
         <v>10</v>
-      </c>
-      <c r="E150" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>849-409-4180</t>
+          <t>809-576-1481</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Milena Yaneth</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D151" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E151" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>849-360-2536</t>
+          <t>849-605-7205</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Alejandro Adrián</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D152" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>849-239-1758</t>
+          <t>849-229-9301</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Blanca González</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D153" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>849-457-8508</t>
+          <t>829-910-5421</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Alexander Juan</t>
+          <t>Fabián Guillermo</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>809-957-8068</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Edwin Leandro</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>15</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>809-935-4233</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Martha Contreras</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>15</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>809-818-9820</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Carlos Jiménez</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>15</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>849-247-5982</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Alonso Felipe</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>15</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>829-841-9868</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Andrea Dayana</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>15</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>849-958-7261</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>María Rivas</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>15</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>829-867-9250</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Antonio Martínez</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>14</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>829-734-1831</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Mónica Rojas</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>14</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>849-985-3749</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Dario Rojas</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>14</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>809-382-5881</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Raquel Alejandra</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>14</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>809-504-7927</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Andrés Alexis</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>14</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>849-979-1026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Diego García</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>13</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>849-806-6720</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Jorge Orlando</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>13</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>809-690-4894</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Beatriz Mariela</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>20</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>829-341-4303</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Patricia Bonilla</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>20</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>809-709-9192</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Esneider Castellanos</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>20</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>849-302-9235</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Esteban Antonio</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>20</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>849-744-8553</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Lilia Ochoa</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>19</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>849-219-3779</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Alba Esmeralda</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>19</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>829-251-6777</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Elena Jenny</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
         <v>18</v>
       </c>
-      <c r="E154" t="n">
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>829-690-5979</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Luis Jesús</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>17</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>849-722-9761</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Jesús Reyes</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>17</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>809-728-9575</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Cecilia Sepúlveda</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>17</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>849-724-5434</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Daniel Perea</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>17</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>829-455-3238</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Daniela Rosa</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>17</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>829-582-3179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Álvaro Vallejo</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>16</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>829-677-1506</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Dary Escobar</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>16</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>809-978-7164</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Edwin Alberto</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>16</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>809-541-1594</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Manuel Alberto</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>16</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>829-955-3967</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>829-925-2215</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>829-376-1995</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>829-632-3645</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="n">
+        <v>6</v>
+      </c>
+      <c r="E187" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>829-899-8785</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>8</v>
+      </c>
+      <c r="E188" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>809-505-6495</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>829-887-5720</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2</v>
+      </c>
+      <c r="D190" t="n">
+        <v>12</v>
+      </c>
+      <c r="E190" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>849-729-2279</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>14</v>
+      </c>
+      <c r="E191" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>829-996-1817</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" t="n">
+        <v>16</v>
+      </c>
+      <c r="E192" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>829-279-1783</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>María Yasmín</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>18</v>
+      </c>
+      <c r="E193" t="n">
         <v>20</v>
       </c>
     </row>

--- a/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/call_center-1000j-100m-2_30tr-same_per_machined-20c_sjf.xlsx
+++ b/AI Planning/Job Scheduling/Job To Machine/problemset/solution/sjf/call_center-1000j-100m-2_30tr-same_per_machined-20c_sjf.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,670 +458,670 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>849-202-1113</t>
+          <t>849-334-6261</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Juan Rubén</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>849-274-9481</t>
+          <t>829-683-2947</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Juan Rubén</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>829-294-6191</t>
+          <t>809-202-4099</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Juan Rubén</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>809-709-3050</t>
+          <t>849-462-8040</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Juan Rubén</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>849-779-8275</t>
+          <t>849-745-6509</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Juan Rubén</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>849-968-1425</t>
+          <t>829-605-1527</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Juan Rubén</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>849-412-5080</t>
+          <t>829-550-3271</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Luz Patricia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>849-311-3144</t>
+          <t>829-317-3464</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Luz Patricia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>849-258-6587</t>
+          <t>849-366-3277</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Luz Patricia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>849-268-8332</t>
+          <t>809-797-1392</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Antonia Lozano</t>
+          <t>Luz Patricia</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>829-277-6961</t>
+          <t>809-211-1772</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Luz Patricia</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>829-272-6537</t>
+          <t>829-740-2311</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Luz Patricia</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>829-251-2094</t>
+          <t>809-643-5353</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>809-536-8060</t>
+          <t>849-721-9458</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>849-772-4638</t>
+          <t>829-385-1523</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>809-641-6553</t>
+          <t>829-476-9224</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>809-973-5635</t>
+          <t>809-380-3391</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>849-252-2435</t>
+          <t>849-711-7758</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>809-939-3000</t>
+          <t>809-224-4105</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>809-252-9356</t>
+          <t>809-707-6261</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandra Díaz</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>829-353-5645</t>
+          <t>829-968-7954</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>809-665-5585</t>
+          <t>849-470-8988</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Brayan Hernán</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>829-811-2282</t>
+          <t>829-898-1629</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Rosa García</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>829-832-9921</t>
+          <t>829-909-9872</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Rosa García</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>809-729-8958</t>
+          <t>849-749-2924</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Rosa García</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>829-609-4354</t>
+          <t>849-361-5850</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Rosa García</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>829-887-3710</t>
+          <t>829-839-9805</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Viviana Ortega</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>829-223-2155</t>
+          <t>849-988-2703</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Viviana Ortega</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>849-771-2410</t>
+          <t>849-947-8048</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Viviana Ortega</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>809-297-1825</t>
+          <t>829-527-5004</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>María Liliana</t>
+          <t>Viviana Ortega</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>849-835-1120</t>
+          <t>849-377-4372</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Viviana Ortega</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>809-467-8488</t>
+          <t>849-429-9204</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Lucía Soto</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>4</v>
@@ -1130,607 +1130,607 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>829-799-5109</t>
+          <t>829-864-9343</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Lucía Soto</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>809-538-5500</t>
+          <t>829-860-1091</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Lucía Soto</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>809-211-1547</t>
+          <t>809-729-7455</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Lucía Soto</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>849-998-8564</t>
+          <t>849-381-3078</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Lucía Soto</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>849-894-9487</t>
+          <t>829-525-6217</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Ángel Jaider</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>849-579-1828</t>
+          <t>829-808-1557</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Ángel Jaider</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>809-251-6515</t>
+          <t>829-283-4673</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Ángel Jaider</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>849-290-2341</t>
+          <t>809-385-7346</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>César Leandro</t>
+          <t>Ángel Jaider</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>829-660-4297</t>
+          <t>849-418-1883</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pablo José</t>
+          <t>Ángel Jaider</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>809-997-5945</t>
+          <t>829-385-4455</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pablo José</t>
+          <t>María Alba</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>849-840-9656</t>
+          <t>829-382-3545</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pablo José</t>
+          <t>María Alba</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>829-665-1843</t>
+          <t>809-356-2979</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pablo José</t>
+          <t>María Alba</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>829-628-7732</t>
+          <t>809-397-8102</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pablo José</t>
+          <t>María Alba</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>829-469-4582</t>
+          <t>809-210-1442</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pablo José</t>
+          <t>Francisco Sierra</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>849-835-7375</t>
+          <t>809-648-1980</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marina Bedoya</t>
+          <t>Francisco Sierra</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>829-234-4994</t>
+          <t>829-568-1255</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marina Bedoya</t>
+          <t>Francisco Sierra</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>809-484-4304</t>
+          <t>849-706-3970</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marina Bedoya</t>
+          <t>Francisco Sierra</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>809-475-3208</t>
+          <t>829-995-4696</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marina Bedoya</t>
+          <t>Jessica Cecilia</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>829-498-9188</t>
+          <t>809-489-9257</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marina Bedoya</t>
+          <t>Jessica Cecilia</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>809-419-1285</t>
+          <t>829-848-3655</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marina Bedoya</t>
+          <t>Jessica Cecilia</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="n">
         <v>15</v>
-      </c>
-      <c r="E53" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>809-265-3383</t>
+          <t>829-421-8365</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nancy Mosquera</t>
+          <t>Jessica Cecilia</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>829-769-1247</t>
+          <t>829-654-9119</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nancy Mosquera</t>
+          <t>Octavio José</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>809-661-3732</t>
+          <t>809-502-1133</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nancy Mosquera</t>
+          <t>Octavio José</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>829-951-5494</t>
+          <t>849-953-1386</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nancy Mosquera</t>
+          <t>Octavio José</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>809-311-8187</t>
+          <t>809-468-8281</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nancy Mosquera</t>
+          <t>Octavio José</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>829-908-4019</t>
+          <t>849-706-7123</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nancy Mosquera</t>
+          <t>Ramón Alfredo</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>849-702-8087</t>
+          <t>809-510-4287</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ángel Jimmy</t>
+          <t>Ramón Alfredo</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>809-584-2136</t>
+          <t>849-855-7475</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ángel Jimmy</t>
+          <t>Cindy Murillo</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>829-970-2885</t>
+          <t>829-538-2516</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ángel Jimmy</t>
+          <t>Cindy Murillo</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
         <v>12</v>
@@ -1739,586 +1739,586 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>829-294-5182</t>
+          <t>829-857-6615</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ángel Jimmy</t>
+          <t>Cindy Murillo</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
         <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>829-308-5214</t>
+          <t>849-899-3402</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ángel Jimmy</t>
+          <t>Marlene Doris</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>829-543-8267</t>
+          <t>849-572-1393</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vanessa Ortiz</t>
+          <t>Marlene Doris</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>809-862-2541</t>
+          <t>849-351-1827</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vanessa Ortiz</t>
+          <t>Marlene Doris</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>849-355-9755</t>
+          <t>829-337-8628</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vanessa Ortiz</t>
+          <t>Tatiana Marta</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>849-648-3768</t>
+          <t>849-739-6829</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vanessa Ortiz</t>
+          <t>Tatiana Marta</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>809-434-9803</t>
+          <t>849-732-1400</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vanessa Ortiz</t>
+          <t>Tatiana Marta</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>849-882-8713</t>
+          <t>849-664-2177</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Leidy María</t>
+          <t>Milena Moreno</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>809-616-7278</t>
+          <t>829-490-9073</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Leidy María</t>
+          <t>Milena Moreno</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>849-938-6757</t>
+          <t>829-267-9558</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Leidy María</t>
+          <t>Milena Moreno</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>829-842-4093</t>
+          <t>829-617-8743</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Leidy María</t>
+          <t>Ángel Pineda</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
         <v>9</v>
-      </c>
-      <c r="E73" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>809-487-7046</t>
+          <t>829-829-8933</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Leidy María</t>
+          <t>Ángel Pineda</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>829-312-4084</t>
+          <t>849-418-1004</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Leidy María</t>
+          <t>Lina García</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>849-328-2144</t>
+          <t>849-568-6102</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Margarita Vásquez</t>
+          <t>Lina García</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>809-876-9960</t>
+          <t>809-987-2133</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Margarita Vásquez</t>
+          <t>Antonio Gómez</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>809-762-6058</t>
+          <t>809-583-5765</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Margarita Vásquez</t>
+          <t>Antonio Gómez</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>829-615-5089</t>
+          <t>849-919-2112</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Margarita Vásquez</t>
+          <t>Enrique Restrepo</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>809-765-1563</t>
+          <t>829-605-8698</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Elizabeth Gabriela</t>
+          <t>Enrique Restrepo</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>849-580-8817</t>
+          <t>829-422-4126</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Elizabeth Gabriela</t>
+          <t>Jhonatan Manuel</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>809-672-7837</t>
+          <t>829-833-9243</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Elizabeth Gabriela</t>
+          <t>Jhonatan Manuel</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>849-590-6829</t>
+          <t>809-870-4129</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Elizabeth Gabriela</t>
+          <t>Orlando Carlos</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>849-991-5841</t>
+          <t>829-539-3005</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Luz Andrea</t>
+          <t>Orlando Carlos</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>829-281-8473</t>
+          <t>849-482-2118</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Luz Andrea</t>
+          <t>Carolina Ortiz</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>809-831-8374</t>
+          <t>849-412-7544</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Luz Andrea</t>
+          <t>Carolina Ortiz</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>849-514-3882</t>
+          <t>829-432-9149</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Luz Andrea</t>
+          <t>Osvaldo Gómez</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>829-981-4957</t>
+          <t>829-262-7523</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Luz Andrea</t>
+          <t>Osvaldo Gómez</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>809-931-2011</t>
+          <t>809-589-7467</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Viviana Sofía</t>
+          <t>Efrain Perdomo</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>849-532-3548</t>
+          <t>829-808-2034</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Viviana Sofía</t>
+          <t>Óscar Antonio</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>12</v>
@@ -2327,334 +2327,334 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>809-731-1919</t>
+          <t>829-680-4598</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Viviana Sofía</t>
+          <t>Paola Yuly</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D91" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>809-777-3301</t>
+          <t>829-211-8494</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>David Arturo</t>
+          <t>Raquel Yazmín</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>849-629-2401</t>
+          <t>809-503-6169</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>David Arturo</t>
+          <t>Damaris Lina</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>849-474-2944</t>
+          <t>829-712-4606</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>David Arturo</t>
+          <t>Jesús Luis</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>849-798-9559</t>
+          <t>809-317-1273</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>María Vanessa</t>
+          <t>Jesús Luis</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>809-333-4387</t>
+          <t>849-510-8522</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>María Vanessa</t>
+          <t>Tatiana Alfonso</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>809-963-8150</t>
+          <t>849-877-5571</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>María Vanessa</t>
+          <t>Tatiana Alfonso</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E97" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>849-913-4195</t>
+          <t>809-341-1747</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alexander Emiro</t>
+          <t>Jesús Jonathan</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>809-503-5785</t>
+          <t>829-533-1516</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alexander Emiro</t>
+          <t>Jesús Jonathan</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E99" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>849-615-8969</t>
+          <t>829-759-8831</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alexander Emiro</t>
+          <t>Luis Ramos</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>849-766-1820</t>
+          <t>849-666-9796</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Efrén Arturo</t>
+          <t>Luis Ramos</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E101" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>829-805-8438</t>
+          <t>849-485-3586</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Efrén Arturo</t>
+          <t>José Marcos</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>829-740-1320</t>
+          <t>829-430-9325</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Efrén Arturo</t>
+          <t>José Marcos</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E103" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>829-723-5351</t>
+          <t>849-822-6653</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Efrén Arturo</t>
+          <t>Camila Liliana</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D104" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>829-766-4425</t>
+          <t>849-918-2777</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sandra Toro</t>
+          <t>Hilda Yésica</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>809-700-4947</t>
+          <t>829-220-3531</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sandra Toro</t>
+          <t>Carolina Ángel</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>16</v>
@@ -2663,40 +2663,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>809-422-5004</t>
+          <t>809-329-3143</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Alcira Lady</t>
+          <t>Adriana Liliana</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>809-217-6734</t>
+          <t>829-717-3007</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Alcira Lady</t>
+          <t>Milena Quintero</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
         <v>14</v>
@@ -2705,40 +2705,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>829-886-7182</t>
+          <t>829-659-4318</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>María Pinzón</t>
+          <t>Juan Jefferson</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D109" t="n">
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>809-464-5828</t>
+          <t>809-209-9199</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>María Pinzón</t>
+          <t>Mario Aldemar</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>14</v>
@@ -2747,166 +2747,166 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>829-972-2695</t>
+          <t>809-929-2493</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Alberto Cerón</t>
+          <t>Jhon Quintero</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>809-390-5337</t>
+          <t>829-915-8823</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alberto Cerón</t>
+          <t>Stella Mariela</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>829-504-5105</t>
+          <t>829-505-4288</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Alberto Cerón</t>
+          <t>Miguel González</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D113" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>849-378-4849</t>
+          <t>809-688-4262</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cindy Shirley</t>
+          <t>Yulieth Murillo</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D114" t="n">
         <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>809-423-8773</t>
+          <t>849-217-5207</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cindy Shirley</t>
+          <t>Rosa Ana</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>849-875-2635</t>
+          <t>829-869-8942</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cindy Shirley</t>
+          <t>Milena Aleida</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D116" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>849-648-9602</t>
+          <t>849-231-4257</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Carlos Trujillo</t>
+          <t>José Esteban</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>829-845-4774</t>
+          <t>809-268-9144</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Carlos Trujillo</t>
+          <t>Germán Acosta</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
         <v>12</v>
@@ -2915,61 +2915,61 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>809-656-6879</t>
+          <t>849-276-9185</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Carlos Trujillo</t>
+          <t>Pablo José</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D119" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>829-671-8478</t>
+          <t>829-253-5565</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Graciela Suárez</t>
+          <t>Marina Cárdenas</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>849-796-9126</t>
+          <t>849-782-7565</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Graciela Suárez</t>
+          <t>Juan Hernández</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
         <v>20</v>
@@ -2978,124 +2978,124 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>809-456-5687</t>
+          <t>809-437-8760</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Juan Mendoza</t>
+          <t>Israel Wilmer</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D122" t="n">
         <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>829-265-5303</t>
+          <t>809-895-5773</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Juan Mendoza</t>
+          <t>Edison Acevedo</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>829-416-2187</t>
+          <t>849-904-2261</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Danilo Cabrera</t>
+          <t>Viviana Delgado</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>809-740-1029</t>
+          <t>829-894-1052</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Danilo Cabrera</t>
+          <t>Vanessa Liliana</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D125" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>849-757-2337</t>
+          <t>849-535-5406</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Martha Mariana</t>
+          <t>John Luis</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>849-966-2621</t>
+          <t>829-977-1231</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Martha Mariana</t>
+          <t>Óscar Giraldo</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>18</v>
@@ -3104,229 +3104,229 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>809-661-1532</t>
+          <t>829-556-1229</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Edgar Rojas</t>
+          <t>David Salazar</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>849-701-1503</t>
+          <t>849-252-7574</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Edgar Rojas</t>
+          <t>María Mendoza</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D129" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>809-769-3219</t>
+          <t>849-627-6589</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Clara Triana</t>
+          <t>Rocío Cabrera</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>849-866-4846</t>
+          <t>809-424-4006</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Clara Triana</t>
+          <t>Carlos Mario</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>809-670-4998</t>
+          <t>809-960-1713</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Andrea Mercedes</t>
+          <t>Eduar Santiago</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>809-760-9774</t>
+          <t>849-535-2707</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Andrea Mercedes</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>809-831-6128</t>
+          <t>829-234-7901</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Francisco Alfonso</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>829-411-3881</t>
+          <t>809-782-8263</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Francisco Alfonso</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D135" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E135" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>849-440-8757</t>
+          <t>829-490-7801</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Luis Ortiz</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>809-736-9065</t>
+          <t>829-298-4557</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Andrea Fuentes</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>809-958-4021</t>
+          <t>829-213-1982</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mónica Ramírez</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E138" t="n">
         <v>12</v>
@@ -3335,1155 +3335,84 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>829-292-6107</t>
+          <t>829-843-7552</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Juliana Sánchez</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E139" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>829-936-6178</t>
+          <t>849-670-1473</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Marcela Blanca</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E140" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>849-295-9152</t>
+          <t>829-268-3604</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Stella María</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>849-570-8617</t>
+          <t>829-591-8604</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ernesto Carlos</t>
+          <t>Martín Carlos</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E142" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>829-970-5050</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Cristian Felipe</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>11</v>
-      </c>
-      <c r="D143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>809-358-3674</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Lucía Guzmán</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>11</v>
-      </c>
-      <c r="D144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>829-696-1890</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>René Gustavo</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>11</v>
-      </c>
-      <c r="D145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>849-229-4319</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Martha María</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>10</v>
-      </c>
-      <c r="D146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>849-565-5904</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Martha María</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>10</v>
-      </c>
-      <c r="D147" t="n">
-        <v>10</v>
-      </c>
-      <c r="E147" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>849-848-9125</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Aurora Marcela</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>10</v>
-      </c>
-      <c r="D148" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>809-790-3766</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Aurora Marcela</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>10</v>
-      </c>
-      <c r="D149" t="n">
-        <v>10</v>
-      </c>
-      <c r="E149" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>849-284-8298</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Milena Yaneth</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>10</v>
-      </c>
-      <c r="D150" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>809-576-1481</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Milena Yaneth</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>10</v>
-      </c>
-      <c r="D151" t="n">
-        <v>10</v>
-      </c>
-      <c r="E151" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>849-605-7205</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Alejandro Adrián</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>15</v>
-      </c>
-      <c r="D152" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>849-229-9301</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Blanca González</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>15</v>
-      </c>
-      <c r="D153" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>829-910-5421</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Fabián Guillermo</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>15</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>809-957-8068</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Edwin Leandro</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>15</v>
-      </c>
-      <c r="D155" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>809-935-4233</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Martha Contreras</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>15</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>809-818-9820</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Carlos Jiménez</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>15</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>849-247-5982</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Alonso Felipe</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>15</v>
-      </c>
-      <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>829-841-9868</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Andrea Dayana</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>15</v>
-      </c>
-      <c r="D159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>849-958-7261</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>María Rivas</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>15</v>
-      </c>
-      <c r="D160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>829-867-9250</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Antonio Martínez</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>14</v>
-      </c>
-      <c r="D161" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>829-734-1831</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Mónica Rojas</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>14</v>
-      </c>
-      <c r="D162" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>849-985-3749</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Dario Rojas</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>14</v>
-      </c>
-      <c r="D163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>809-382-5881</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Raquel Alejandra</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>14</v>
-      </c>
-      <c r="D164" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>809-504-7927</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Andrés Alexis</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>14</v>
-      </c>
-      <c r="D165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>849-979-1026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Diego García</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>13</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>849-806-6720</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Jorge Orlando</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>13</v>
-      </c>
-      <c r="D167" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>809-690-4894</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Beatriz Mariela</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>20</v>
-      </c>
-      <c r="D168" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>829-341-4303</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Patricia Bonilla</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>20</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>809-709-9192</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Esneider Castellanos</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
-        <v>20</v>
-      </c>
-      <c r="D170" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>849-302-9235</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Esteban Antonio</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
-        <v>20</v>
-      </c>
-      <c r="D171" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>849-744-8553</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Lilia Ochoa</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
-        <v>19</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>849-219-3779</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Alba Esmeralda</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
-        <v>19</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>829-251-6777</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Elena Jenny</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
-        <v>18</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>829-690-5979</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Luis Jesús</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
-        <v>17</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>849-722-9761</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Jesús Reyes</t>
-        </is>
-      </c>
-      <c r="C176" t="n">
-        <v>17</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>809-728-9575</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Cecilia Sepúlveda</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>17</v>
-      </c>
-      <c r="D177" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>849-724-5434</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Daniel Perea</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>17</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>829-455-3238</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Daniela Rosa</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>17</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>829-582-3179</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Álvaro Vallejo</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>16</v>
-      </c>
-      <c r="D180" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>829-677-1506</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Dary Escobar</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>16</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>809-978-7164</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Edwin Alberto</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>16</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>809-541-1594</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Manuel Alberto</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>16</v>
-      </c>
-      <c r="D183" t="n">
-        <v>0</v>
-      </c>
-      <c r="E183" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>829-955-3967</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C184" t="n">
-        <v>2</v>
-      </c>
-      <c r="D184" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>829-925-2215</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>2</v>
-      </c>
-      <c r="D185" t="n">
-        <v>2</v>
-      </c>
-      <c r="E185" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>829-376-1995</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>2</v>
-      </c>
-      <c r="D186" t="n">
-        <v>4</v>
-      </c>
-      <c r="E186" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>829-632-3645</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>2</v>
-      </c>
-      <c r="D187" t="n">
-        <v>6</v>
-      </c>
-      <c r="E187" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>829-899-8785</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>2</v>
-      </c>
-      <c r="D188" t="n">
-        <v>8</v>
-      </c>
-      <c r="E188" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>809-505-6495</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>2</v>
-      </c>
-      <c r="D189" t="n">
-        <v>10</v>
-      </c>
-      <c r="E189" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>829-887-5720</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>2</v>
-      </c>
-      <c r="D190" t="n">
-        <v>12</v>
-      </c>
-      <c r="E190" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>849-729-2279</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>2</v>
-      </c>
-      <c r="D191" t="n">
-        <v>14</v>
-      </c>
-      <c r="E191" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>829-996-1817</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>2</v>
-      </c>
-      <c r="D192" t="n">
-        <v>16</v>
-      </c>
-      <c r="E192" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>829-279-1783</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>María Yasmín</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>2</v>
-      </c>
-      <c r="D193" t="n">
-        <v>18</v>
-      </c>
-      <c r="E193" t="n">
         <v>20</v>
       </c>
     </row>
